--- a/docs/raw_input_data_table.xlsx
+++ b/docs/raw_input_data_table.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://seforallorg.sharepoint.com/Middle-Earth/Shared Documents/3. Team Folders/Policy/UIEP/1. Activities/H. Center of Excellence/5. Data &amp; Tools/IEP Cooling Component/MDG/AgCAP MDG - deploy folder/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="267" documentId="8_{53B8EE6F-FDB7-4160-8946-61F8CE9E97DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DB980ECC-867C-452D-8AF8-3BAA390A87F5}"/>
+  <xr:revisionPtr revIDLastSave="278" documentId="8_{53B8EE6F-FDB7-4160-8946-61F8CE9E97DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8C7B2422-5DA6-4D7B-9219-893EA6D259C5}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" xr2:uid="{877A706C-C57B-4FA4-8A66-B89DBD743672}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="125">
   <si>
     <t>Dataset Name</t>
   </si>
@@ -438,9 +438,6 @@
     <t>https://globalsolaratlas.info/download</t>
   </si>
   <si>
-    <t>Generated by the auxiliary tool provided, starting from CSV files (one for each POI, having only 2 columns: X_COORD, Y_COORD). Based on https://malariaatlas.org/project-resources/accessibility-to-healthcare/</t>
-  </si>
-  <si>
     <t>https://malariaatlas.org/project-resources/accessibility-to-healthcare/</t>
   </si>
   <si>
@@ -477,9 +474,6 @@
     <t>https://overpass-turbo.eu/?Q=%2F*%0AThis%20query%20looks%20for%20nodes%2C%20ways%2C%20and%20relations%20%0Atagged%20as%20%27railway%3Dstation%27%20or%20%27railway%3Dhalt%27%20%0Awithin%20the%20area%20of%20Madagascar.%0A*%2F%0A%0A%5Bout%3Ajson%5D%5Btimeout%3A25%5D%3B%0A%0A%2F%2F%20fetch%20area%20%E2%80%9CMadagascar%E2%80%9D%20to%20search%20in%0A%7B%7BgeocodeArea%3AMadagascar%7D%7D-%3E.searchArea%3B%0A%0A%2F%2F%20gather%20results%0A%28%0A%20%20%2F%2F%20query%20for%20stations%0A%20%20node%5B%22railway%22%3D%22station%22%5D%28area.searchArea%29%3B%0A%20%20way%5B%22railway%22%3D%22station%22%5D%28area.searchArea%29%3B%0A%20%20relation%5B%22railway%22%3D%22station%22%5D%28area.searchArea%29%3B%0A%0A%20%20%2F%2F%20query%20for%20smaller%20halts%20%28optional%2C%20but%20recommended%29%0A%20%20node%5B%22railway%22%3D%22halt%22%5D%28area.searchArea%29%3B%0A%20%20way%5B%22railway%22%3D%22halt%22%5D%28area.searchArea%29%3B%0A%20%20relation%5B%22railway%22%3D%22halt%22%5D%28area.searchArea%29%3B%0A%29%3B%0A%0A%2F%2F%20print%20results%0Aout%20geom%3B&amp;C=-20.092272%3B48.051011%3B8&amp;R=</t>
   </si>
   <si>
-    <t>To be checked and cleaned before ingestion</t>
-  </si>
-  <si>
     <t>https://overpass-turbo.eu/?Q=%2F*%0AThis%20query%20looks%20for%20nodes%2C%20ways%2C%20and%20relations%20%0Atagged%20as%20%27industrial%3Dport%27%20%28commercial%20ports%29%20%0Aor%20%27harbour%27%20%28general%20harbors%29%20in%20Madagascar.%0A*%2F%0A%0A%5Bout%3Ajson%5D%5Btimeout%3A25%5D%3B%0A%0A%2F%2F%20fetch%20area%20%E2%80%9CMadagascar%E2%80%9D%0A%7B%7BgeocodeArea%3AMadagascar%7D%7D-%3E.searchArea%3B%0A%0A%2F%2F%20gather%20results%0A%28%0A%20%20%2F%2F%201.%20Search%20for%20industrial%20port%20areas%20%28best%20for%20main%20commercial%20ports%29%0A%20%20node%5B%22industrial%22%3D%22port%22%5D%28area.searchArea%29%3B%0A%20%20way%5B%22industrial%22%3D%22port%22%5D%28area.searchArea%29%3B%0A%20%20relation%5B%22industrial%22%3D%22port%22%5D%28area.searchArea%29%3B%0A%0A%20%20%2F%2F%202.%20Search%20for%20general%20harbor%20nodes%2Fareas%0A%20%20node%5B%22harbour%22%5D%28area.searchArea%29%3B%0A%20%20way%5B%22harbour%22%5D%28area.searchArea%29%3B%0A%20%20relation%5B%22harbour%22%5D%28area.searchArea%29%3B%0A%29%3B%0A%0A%2F%2F%20print%20results%20with%20geometry%0Aout%20geom%3B&amp;C=-20.386531%3B49.205028%3B6&amp;R=</t>
   </si>
   <si>
@@ -508,6 +502,15 @@
   </si>
   <si>
     <t>https://overpass-turbo.eu/?q=LyoKVGhpcyBxdWVyeSBzZWxlY3TEhmFsbCB3YXnEhnRhZ2dlZCAnbmF0dXLElT1jb2FzdGxpbmUnIAp3aXTEhG4gxLplIGFkbcSyxIV0xKl0aXbEv2JvdW5kYcSLIG9mIE3FgcSexK5jxZEuCiovCgpbxY10Ompzb25dW8WIbWXFpDo2MF07IC8vIEluY3JlxK7EocS9acWuxaQgZm9yIHBvdGVuxYjElWzEjGzFkcSgxIfEicSLxaHFtyBGxLLEosS-xYDFgsWExK_Fh8WJxL_FkcW-xoXGh8WWxZhnxZrFkQp7e8Sgb8SsZGVBxb1hOsWXxZDGrXPFm3J9fS0-LsSOxZFjaMa4xb47xpnFuEfEpmjEisWAxJbEmMSaxJzEnsSgxKLEpcSnxKlsxKvErcSvxLHEsyDEsnNpxrbEvceSxYDGucS3xJpbIsecxKjElSI9IsSsxK7EsMSyZSJdKManYceGxb5yx4nHi2Epx40KxppQcsSydCDFvXN1bMSTxJjEuWggxrPFrsWGeQrGhMiaOw&amp;c=Bc3iYSOD8G&amp;R=</t>
+  </si>
+  <si>
+    <t>To be converted into raster GeoTIFF using the auxiliary tool provided</t>
+  </si>
+  <si>
+    <t>To be processed to calculate accessibility (travel time) raster files, using the auxiliary tool provided</t>
+  </si>
+  <si>
+    <t>Generated by the dedicated auxiliary tool provided, starting from POIs</t>
   </si>
 </sst>
 </file>
@@ -1151,7 +1154,7 @@
         <v>36</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>1</v>
@@ -1222,21 +1225,21 @@
         <v>61</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" ht="42.45">
       <c r="A4" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>39</v>
@@ -1245,7 +1248,9 @@
         <f t="shared" si="0"/>
         <v>[Open Street Map Airports](https://overpass-turbo.eu/?Q=%2F*%0AThis%20query%20looks%20for%20nodes%2C%20ways%2C%20and%20relations%20%0Atagged%20as%20%27aeroway%3Daerodrome%27%20%28airports%2Fairstrips%29%20%0Ain%20Madagascar.%0A*%2F%0A%0A%5Bout%3Ajson%5D%5Btimeout%3A25%5D%3B%0A%0A%2F%2F%20fetch%20area%20%E2%80%9CMadagascar%E2%80%9D%0A%7B%7BgeocodeArea%3AMadagascar%7D%7D-%3E.searchArea%3B%0A%0A%2F%2F%20gather%20results%0A%28%0A%20%20%2F%2F%20Search%20for%20airports%20mapped%20as%20points%20%28nodes%29%0A%20%20node%5B%22aeroway%22%3D%22aerodrome%22%5D%28area.searchArea%29%3B%0A%20%20%0A%20%20%2F%2F%20Search%20for%20airports%20mapped%20as%20outlines%2Fpolygons%20%28ways%2Frelations%29%0A%20%20way%5B%22aeroway%22%3D%22aerodrome%22%5D%28area.searchArea%29%3B%0A%20%20relation%5B%22aeroway%22%3D%22aerodrome%22%5D%28area.searchArea%29%3B%0A%29%3B%0A%0A%2F%2F%20print%20results%20with%20geometry%0Aout%20geom%3B&amp;C=-19.642037%3B49.774223%3B6&amp;R=)</v>
       </c>
-      <c r="H4" s="2"/>
+      <c r="H4" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="5" spans="1:8" ht="42.45">
       <c r="A5" s="1" t="s">
@@ -1421,7 +1426,7 @@
         <v>78</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D11" s="5" t="str">
         <f>HYPERLINK(Table1[[#This Row],[Link for download]],Table1[[#This Row],[Source]])</f>
@@ -1541,7 +1546,7 @@
         <v>2</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G15" s="3" t="str">
         <f t="shared" si="0"/>
@@ -1634,10 +1639,10 @@
         <v>23</v>
       </c>
       <c r="B19" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="D19" s="5" t="str">
         <f>HYPERLINK(Table1[[#This Row],[Link for download]],Table1[[#This Row],[Source]])</f>
@@ -1655,21 +1660,21 @@
       </c>
       <c r="H19" s="2"/>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" ht="42.45">
       <c r="A20" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>39</v>
@@ -1678,7 +1683,9 @@
         <f t="shared" si="0"/>
         <v>[Open Street Map Ports](https://overpass-turbo.eu/?Q=%2F*%0AThis%20query%20looks%20for%20nodes%2C%20ways%2C%20and%20relations%20%0Atagged%20as%20%27industrial%3Dport%27%20%28commercial%20ports%29%20%0Aor%20%27harbour%27%20%28general%20harbors%29%20in%20Madagascar.%0A*%2F%0A%0A%5Bout%3Ajson%5D%5Btimeout%3A25%5D%3B%0A%0A%2F%2F%20fetch%20area%20%E2%80%9CMadagascar%E2%80%9D%0A%7B%7BgeocodeArea%3AMadagascar%7D%7D-%3E.searchArea%3B%0A%0A%2F%2F%20gather%20results%0A%28%0A%20%20%2F%2F%201.%20Search%20for%20industrial%20port%20areas%20%28best%20for%20main%20commercial%20ports%29%0A%20%20node%5B%22industrial%22%3D%22port%22%5D%28area.searchArea%29%3B%0A%20%20way%5B%22industrial%22%3D%22port%22%5D%28area.searchArea%29%3B%0A%20%20relation%5B%22industrial%22%3D%22port%22%5D%28area.searchArea%29%3B%0A%0A%20%20%2F%2F%202.%20Search%20for%20general%20harbor%20nodes%2Fareas%0A%20%20node%5B%22harbour%22%5D%28area.searchArea%29%3B%0A%20%20way%5B%22harbour%22%5D%28area.searchArea%29%3B%0A%20%20relation%5B%22harbour%22%5D%28area.searchArea%29%3B%0A%29%3B%0A%0A%2F%2F%20print%20results%20with%20geometry%0Aout%20geom%3B&amp;C=-20.386531%3B49.205028%3B6&amp;R=)</v>
       </c>
-      <c r="H20" s="2"/>
+      <c r="H20" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="21" spans="1:8" ht="113.15">
       <c r="A21" s="1" t="s">
@@ -1734,21 +1741,21 @@
       </c>
       <c r="H22" s="2"/>
     </row>
-    <row r="23" spans="1:8" ht="28.3">
+    <row r="23" spans="1:8" ht="42.45">
       <c r="A23" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>39</v>
@@ -1758,7 +1765,7 @@
         <v>[Open Street Map Railway Stations](https://overpass-turbo.eu/?Q=%2F*%0AThis%20query%20looks%20for%20nodes%2C%20ways%2C%20and%20relations%20%0Atagged%20as%20%27railway%3Dstation%27%20or%20%27railway%3Dhalt%27%20%0Awithin%20the%20area%20of%20Madagascar.%0A*%2F%0A%0A%5Bout%3Ajson%5D%5Btimeout%3A25%5D%3B%0A%0A%2F%2F%20fetch%20area%20%E2%80%9CMadagascar%E2%80%9D%20to%20search%20in%0A%7B%7BgeocodeArea%3AMadagascar%7D%7D-%3E.searchArea%3B%0A%0A%2F%2F%20gather%20results%0A%28%0A%20%20%2F%2F%20query%20for%20stations%0A%20%20node%5B%22railway%22%3D%22station%22%5D%28area.searchArea%29%3B%0A%20%20way%5B%22railway%22%3D%22station%22%5D%28area.searchArea%29%3B%0A%20%20relation%5B%22railway%22%3D%22station%22%5D%28area.searchArea%29%3B%0A%0A%20%20%2F%2F%20query%20for%20smaller%20halts%20%28optional%2C%20but%20recommended%29%0A%20%20node%5B%22railway%22%3D%22halt%22%5D%28area.searchArea%29%3B%0A%20%20way%5B%22railway%22%3D%22halt%22%5D%28area.searchArea%29%3B%0A%20%20relation%5B%22railway%22%3D%22halt%22%5D%28area.searchArea%29%3B%0A%29%3B%0A%0A%2F%2F%20print%20results%0Aout%20geom%3B&amp;C=-20.092272%3B48.051011%3B8&amp;R=)</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>113</v>
+        <v>123</v>
       </c>
     </row>
     <row r="24" spans="1:8" ht="42.45">
@@ -1813,7 +1820,9 @@
         <f t="shared" si="0"/>
         <v>[Meta's Relative Wealth Index Map](https://data.humdata.org/dataset/relative-wealth-index?fbclid=IwZXh0bgNhZW0CMTEAYnJpZBExMHp4QTY3ellmaFg2c0dER3NydGMGYXBwX2lkATAAAR5CYAQfvmSSPSh2JLrDT8sebiJEC1jmH-9_HB05sAcSi8fQx947oY87GUzyig_aem_l0P1tM-UMYF3heZ2Fp419A)</v>
       </c>
-      <c r="H25" s="2"/>
+      <c r="H25" s="2" t="s">
+        <v>122</v>
+      </c>
     </row>
     <row r="26" spans="1:8" ht="28.3">
       <c r="A26" s="1" t="s">
@@ -1848,7 +1857,7 @@
         <v>29</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>30</v>
@@ -1879,7 +1888,7 @@
         <v>99</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D28" s="5" t="str">
         <f>HYPERLINK(Table1[[#This Row],[Link for download]],Table1[[#This Row],[Source]])</f>
@@ -1897,15 +1906,15 @@
       </c>
       <c r="H28" s="2"/>
     </row>
-    <row r="29" spans="1:8" ht="84.9">
+    <row r="29" spans="1:8" ht="29.15">
       <c r="A29" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B29" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="D29" s="5" t="str">
         <f>HYPERLINK(Table1[[#This Row],[Link for download]],Table1[[#This Row],[Source]])</f>
@@ -1922,15 +1931,15 @@
         <v>[Travel times to Airports, Ports, Capital, Cities, Railways](https://malariaatlas.org/project-resources/accessibility-to-healthcare/)</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="120.9" customHeight="1">
       <c r="A30" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>33</v>
@@ -1950,7 +1959,7 @@
         <v>[JRC Global Surface Water (GSW)](https://developers.google.com/earth-engine/datasets/catalog/JRC_GSW1_4_GlobalSurfaceWater)</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
   </sheetData>
@@ -2006,15 +2015,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010071561D1A5621A2498CEC3D8456AF0272" ma:contentTypeVersion="23" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="673ae7116fe741eba857aa140154d293">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d" xmlns:ns3="418c1687-f2b4-4c60-bff4-9f013a1b0e9b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1d91f7a8935eb54ad5101523981e9c0e" ns2:_="" ns3:_="">
     <xsd:import namespace="dd8682f3-14aa-4a86-bc0b-a7c76dafad6d"/>
@@ -2299,6 +2299,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{80AD1BE0-AD7B-442D-A04B-E0F6AD5F431F}">
   <ds:schemaRefs>
@@ -2317,14 +2326,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE1B351-0596-4C3C-85C1-37E39234270C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{307F9656-75CD-4FE8-B440-A891FFC37FF8}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -2341,4 +2342,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4DE1B351-0596-4C3C-85C1-37E39234270C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>